--- a/templates/Шаблон_спецификации_РД.xlsx
+++ b/templates/Шаблон_спецификации_РД.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">ГОСТ</t>
   </si>
   <si>
-    <t xml:space="preserve">Наименовние</t>
+    <t xml:space="preserve">Наименование</t>
   </si>
   <si>
     <t xml:space="preserve">Область применения</t>
@@ -234,51 +234,51 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -607,7 +607,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="12" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8"/>
       <c r="B3" s="9"/>
       <c r="C3" s="10"/>
@@ -619,7 +619,7 @@
       <c r="I3" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0"/>
+      <c r="B8" s="12"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:I2"/>
@@ -642,9 +642,9 @@
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="83.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="67.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="12" width="35.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="83.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="67.01"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/templates/Шаблон_спецификации_РД.xlsx
+++ b/templates/Шаблон_спецификации_РД.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Спецификация" sheetId="1" state="visible" r:id="rId3"/>

--- a/templates/Шаблон_спецификации_РД.xlsx
+++ b/templates/Шаблон_спецификации_РД.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Спецификация" sheetId="1" state="visible" r:id="rId3"/>
